--- a/public/data/employees20250105164648.xlsx
+++ b/public/data/employees20250105164648.xlsx
@@ -1,21 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\inan-awards\public\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF3E778-8449-4E0B-9740-30E1FD7C7D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="53">
   <si>
     <t>#</t>
   </si>
@@ -29,164 +50,159 @@
     <t>Employment Type</t>
   </si>
   <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Reporting To</t>
+  </si>
+  <si>
+    <t>Joining Date</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Abisoye Adebayo</t>
+  </si>
+  <si>
+    <t>abisoye.adebayo@inan.com.ng</t>
+  </si>
+  <si>
+    <t>Alfonzo Osunde</t>
+  </si>
+  <si>
+    <t>2024-09-29</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Constance Nwobueze</t>
+  </si>
+  <si>
+    <t>constance.nwobueze@inan.com.ng</t>
+  </si>
+  <si>
+    <t>Philomena Fadipe</t>
+  </si>
+  <si>
+    <t>Samuel Joseph</t>
+  </si>
+  <si>
+    <t>akpo.joseph@inan.com.ng</t>
+  </si>
+  <si>
+    <t>Udoh  Anderson</t>
+  </si>
+  <si>
+    <t>2024-09-17</t>
+  </si>
+  <si>
+    <t>Mercy Igbomoji</t>
+  </si>
+  <si>
+    <t>mercy.igbomoji@inan.com.ng</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>2024-09-09</t>
+  </si>
+  <si>
+    <t>Sokari Andrew-Jaja</t>
+  </si>
+  <si>
+    <t>sokari.jaja@inan.com.ng</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>On Probation</t>
+  </si>
+  <si>
+    <t>Chinedu Onwujuba</t>
+  </si>
+  <si>
+    <t>Chinedu.Onwujuba@inan.com.ng</t>
+  </si>
+  <si>
+    <t>2024-08-02</t>
+  </si>
+  <si>
+    <t>hr@inan.com.ng</t>
+  </si>
+  <si>
+    <t>App Administrator</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>Joseph Olivia Iyabo</t>
+  </si>
+  <si>
+    <t>Olivia.joseph@inan.com.ng</t>
+  </si>
+  <si>
+    <t>Ifeanyi  Chioma</t>
+  </si>
+  <si>
+    <t>chioma.ifeanyi@inan.com.ng</t>
+  </si>
+  <si>
+    <t>Richard Nwidum Goeffrey</t>
+  </si>
+  <si>
+    <t>richard.geoffrey@inan.com.ng</t>
+  </si>
+  <si>
+    <t>Gloria  Ugochi Osunde</t>
+  </si>
+  <si>
+    <t>gloria.osunde@inan.com.ng</t>
+  </si>
+  <si>
+    <t>philomena.fadipe@inan.com.ng</t>
+  </si>
+  <si>
+    <t>Chialuka Martha  Anokwuru</t>
+  </si>
+  <si>
+    <t>martha.anokwuru@inan.com.ng</t>
+  </si>
+  <si>
+    <t>anderson.udoh@inan.com.ng</t>
+  </si>
+  <si>
+    <t>Esther  Chinasa  Ama</t>
+  </si>
+  <si>
+    <t>ESTHER.AMA@inan.com.ng</t>
+  </si>
+  <si>
+    <t>EMP-3</t>
+  </si>
+  <si>
+    <t>alfonzo.osunde@inan.com.ng</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
     <t>Employee</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>Reporting To</t>
-  </si>
-  <si>
-    <t>Joining Date</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Abisoye Adebayo</t>
-  </si>
-  <si>
-    <t>abisoye.adebayo@inan.com.ng</t>
-  </si>
-  <si>
-    <t>Alfonzo Osunde</t>
-  </si>
-  <si>
-    <t>2024-09-29</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Constance Nwobueze</t>
-  </si>
-  <si>
-    <t>constance.nwobueze@inan.com.ng</t>
-  </si>
-  <si>
-    <t>Philomena Fadipe</t>
-  </si>
-  <si>
-    <t>Samuel Joseph</t>
-  </si>
-  <si>
-    <t>akpo.joseph@inan.com.ng</t>
-  </si>
-  <si>
-    <t>Udoh  Anderson</t>
-  </si>
-  <si>
-    <t>2024-09-17</t>
-  </si>
-  <si>
-    <t>Mercy Igbomoji</t>
-  </si>
-  <si>
-    <t>mercy.igbomoji@inan.com.ng</t>
-  </si>
-  <si>
-    <t>Human Resources</t>
-  </si>
-  <si>
-    <t>2024-09-09</t>
-  </si>
-  <si>
-    <t>Sokari Andrew-Jaja</t>
-  </si>
-  <si>
-    <t>sokari.jaja@inan.com.ng</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>On Probation</t>
-  </si>
-  <si>
-    <t>Chinedu Onwujuba</t>
-  </si>
-  <si>
-    <t>Chinedu.Onwujuba@inan.com.ng</t>
-  </si>
-  <si>
-    <t>2024-08-02</t>
-  </si>
-  <si>
-    <t>hr@inan.com.ng</t>
-  </si>
-  <si>
-    <t>App Administrator</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>Joseph Olivia Iyabo</t>
-  </si>
-  <si>
-    <t>Olivia.joseph@inan.com.ng</t>
-  </si>
-  <si>
-    <t>Ifeanyi  Chioma</t>
-  </si>
-  <si>
-    <t>chioma.ifeanyi@inan.com.ng</t>
-  </si>
-  <si>
-    <t>Richard Nwidum Goeffrey</t>
-  </si>
-  <si>
-    <t>richard.geoffrey@inan.com.ng</t>
-  </si>
-  <si>
-    <t>Gloria  Ugochi Osunde</t>
-  </si>
-  <si>
-    <t>gloria.osunde@inan.com.ng</t>
-  </si>
-  <si>
-    <t>philomena.fadipe@inan.com.ng</t>
-  </si>
-  <si>
-    <t>Chialuka Martha  Anokwuru</t>
-  </si>
-  <si>
-    <t>martha.anokwuru@inan.com.ng</t>
-  </si>
-  <si>
-    <t>anderson.udoh@inan.com.ng</t>
-  </si>
-  <si>
-    <t>Esther  Chinasa  Ama</t>
-  </si>
-  <si>
-    <t>ESTHER.AMA@inan.com.ng</t>
-  </si>
-  <si>
-    <t>EMP-3</t>
-  </si>
-  <si>
-    <t>alfonzo.osunde@inan.com.ng</t>
-  </si>
-  <si>
-    <t>--</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -213,13 +229,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -509,14 +533,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="30.44140625" customWidth="1"/>
+    <col min="4" max="4" width="38.77734375" customWidth="1"/>
+    <col min="5" max="5" width="31.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -530,25 +556,25 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -559,22 +585,22 @@
         <v>19</v>
       </c>
       <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
       <c r="J2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -585,22 +611,22 @@
         <v>17</v>
       </c>
       <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -611,22 +637,22 @@
         <v>18</v>
       </c>
       <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>19</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>20</v>
       </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
       <c r="J4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -637,22 +663,22 @@
         <v>16</v>
       </c>
       <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
         <v>22</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>23</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>24</v>
       </c>
-      <c r="I5" t="s">
-        <v>25</v>
-      </c>
       <c r="J5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -663,22 +689,22 @@
         <v>15</v>
       </c>
       <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
         <v>26</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
         <v>27</v>
       </c>
-      <c r="H6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" t="s">
-        <v>28</v>
-      </c>
       <c r="J6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -689,25 +715,25 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>30</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" t="s">
         <v>31</v>
       </c>
-      <c r="H7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" t="s">
-        <v>32</v>
-      </c>
       <c r="J7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -718,25 +744,25 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
         <v>33</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" t="s">
         <v>34</v>
       </c>
-      <c r="H8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" t="s">
-        <v>35</v>
-      </c>
       <c r="J8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -747,22 +773,22 @@
         <v>9</v>
       </c>
       <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" t="s">
         <v>36</v>
       </c>
-      <c r="F9" t="s">
-        <v>37</v>
-      </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -773,22 +799,22 @@
         <v>8</v>
       </c>
       <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" t="s">
         <v>38</v>
       </c>
-      <c r="F10" t="s">
-        <v>39</v>
-      </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -799,22 +825,22 @@
         <v>7</v>
       </c>
       <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
         <v>40</v>
       </c>
-      <c r="F11" t="s">
-        <v>41</v>
-      </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -825,22 +851,22 @@
         <v>6</v>
       </c>
       <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
         <v>42</v>
       </c>
-      <c r="F12" t="s">
-        <v>43</v>
-      </c>
       <c r="H12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -851,22 +877,22 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -877,22 +903,22 @@
         <v>4</v>
       </c>
       <c r="E14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" t="s">
         <v>45</v>
       </c>
-      <c r="F14" t="s">
-        <v>46</v>
-      </c>
       <c r="H14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -903,22 +929,22 @@
         <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -929,22 +955,22 @@
         <v>2</v>
       </c>
       <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" t="s">
         <v>48</v>
       </c>
-      <c r="F16" t="s">
-        <v>49</v>
-      </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -952,39 +978,28 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
         <v>50</v>
       </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" t="s">
         <v>51</v>
       </c>
-      <c r="G17" t="s">
+      <c r="I17" t="s">
         <v>34</v>
       </c>
-      <c r="H17" t="s">
-        <v>52</v>
-      </c>
-      <c r="I17" t="s">
-        <v>35</v>
-      </c>
       <c r="J17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>